--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20260107_201615.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20260107_201615.xlsx
@@ -7658,7 +7658,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7734,7 +7734,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7810,7 +7810,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
